--- a/data/input_profil.xlsx
+++ b/data/input_profil.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krizova\Documents\R\02 cenoveKalkukacky\_vyvoj\vstupy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krizova\Documents\R\02 cenoveKalkukacky\ZP\ZP_shiny_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E81F7A1-4E9D-4E31-A947-F9C12706FB11}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C4D5CE-5335-4EFE-8540-06DCAD4F4F1F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="30720" windowHeight="13284" xr2:uid="{BBC83CC2-0082-439C-9EA0-65C59A271A96}"/>
   </bookViews>
   <sheets>
-    <sheet name="jmena sloupcu" sheetId="13" r:id="rId1"/>
-    <sheet name="PRODUKCE" sheetId="2" r:id="rId2"/>
+    <sheet name="PRODUKCE" sheetId="2" r:id="rId1"/>
+    <sheet name="jmena sloupcu" sheetId="13" r:id="rId2"/>
     <sheet name="data mimo rozsah" sheetId="12" r:id="rId3"/>
     <sheet name="zaporne" sheetId="11" r:id="rId4"/>
     <sheet name="duplicity" sheetId="10" r:id="rId5"/>
@@ -412,7 +412,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{121C41C6-7EC9-4B10-9F7A-07653AA32ACF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6A8899E-8022-459D-93F4-65FB2D6CF524}">
   <dimension ref="A1:B49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -421,11 +421,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>4</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1875,7 +1875,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6A8899E-8022-459D-93F4-65FB2D6CF524}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{121C41C6-7EC9-4B10-9F7A-07653AA32ACF}">
   <dimension ref="A1:B49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1884,11 +1884,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
